--- a/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB LA MATANZA.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CB LA MATANZA.xlsx
@@ -565,13 +565,13 @@
         <v>25</v>
       </c>
       <c r="D2" t="n">
-        <v>22.8293</v>
+        <v>6.2472</v>
       </c>
       <c r="E2" t="n">
-        <v>33.588</v>
+        <v>17.0615</v>
       </c>
       <c r="F2" t="n">
-        <v>-10.7587</v>
+        <v>-10.8142</v>
       </c>
       <c r="G2" t="n">
         <v>-7.589500000000001</v>
@@ -610,13 +610,13 @@
         <v>19.1148</v>
       </c>
       <c r="S2" t="n">
-        <v>28.5448</v>
+        <v>11.9627</v>
       </c>
       <c r="T2" t="n">
-        <v>26.1116</v>
+        <v>9.5852</v>
       </c>
       <c r="U2" t="n">
-        <v>2.4331</v>
+        <v>2.3777</v>
       </c>
       <c r="V2" t="n">
         <v>-4.3046</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. PARRONDO CASTRO</t>
+          <t>L. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -640,76 +640,76 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>26</v>
+        <v>3</v>
       </c>
       <c r="D3" t="n">
-        <v>13.0732</v>
+        <v>1.0313</v>
       </c>
       <c r="E3" t="n">
-        <v>29.3959</v>
+        <v>1.5017</v>
       </c>
       <c r="F3" t="n">
-        <v>-16.3225</v>
+        <v>-0.4704</v>
       </c>
       <c r="G3" t="n">
-        <v>-3.537199999999999</v>
+        <v>0.7072000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>3.9355</v>
+        <v>2.0613</v>
       </c>
       <c r="I3" t="n">
-        <v>-7.472700000000001</v>
+        <v>-1.3542</v>
       </c>
       <c r="J3" t="n">
-        <v>48.3692</v>
+        <v>1.5639</v>
       </c>
       <c r="K3" t="n">
-        <v>40.5783</v>
+        <v>2.1313</v>
       </c>
       <c r="L3" t="n">
-        <v>7.7912</v>
+        <v>-0.5674</v>
       </c>
       <c r="M3" t="n">
-        <v>-51.9066</v>
+        <v>-0.8567</v>
       </c>
       <c r="N3" t="n">
-        <v>-36.6428</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="O3" t="n">
-        <v>-15.2636</v>
+        <v>-0.7867999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>-17.7632</v>
+        <v>0.3862000000000001</v>
       </c>
       <c r="Q3" t="n">
-        <v>-59.4683</v>
+        <v>-1.1585</v>
       </c>
       <c r="R3" t="n">
-        <v>41.7046</v>
+        <v>1.5447</v>
       </c>
       <c r="S3" t="n">
-        <v>18.1774</v>
+        <v>-0.06200000000000003</v>
       </c>
       <c r="T3" t="n">
-        <v>12.4536</v>
+        <v>-0.1314</v>
       </c>
       <c r="U3" t="n">
-        <v>5.7236</v>
+        <v>0.06950000000000002</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1961</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>28.0407</v>
+        <v>1.2277</v>
       </c>
       <c r="X3" t="n">
-        <v>-11.8447</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. FLORES LUCAS</t>
+          <t>A. DELGADO LUIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5746</v>
+        <v>-1.1318</v>
       </c>
       <c r="E4" t="n">
-        <v>1.6051</v>
+        <v>-1.0489</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0305</v>
+        <v>-0.0829</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7072000000000001</v>
+        <v>-0.0423</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0613</v>
+        <v>0.3172</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.3542</v>
+        <v>-0.3595</v>
       </c>
       <c r="J4" t="n">
-        <v>1.5639</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>2.1313</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5674</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8567</v>
+        <v>-0.1244</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.2758</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7867999999999999</v>
+        <v>-0.4002</v>
       </c>
       <c r="P4" t="n">
-        <v>0.3862000000000001</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5447</v>
+        <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5187</v>
+        <v>-0.3172</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.02790000000000001</v>
+        <v>-0.1655</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4907</v>
+        <v>-0.1516</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.2277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DELGADO LUIS</t>
+          <t>J. PARRONDO CASTRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,76 +796,76 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2063</v>
+        <v>-1.614299999999999</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0489</v>
+        <v>18.0751</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1574</v>
+        <v>-19.6893</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0423</v>
+        <v>-3.537199999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3172</v>
+        <v>3.9355</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3595</v>
+        <v>-7.472700000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08210000000000001</v>
+        <v>48.3692</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>40.5783</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>7.7912</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1244</v>
+        <v>-51.9066</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2758</v>
+        <v>-36.6428</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4002</v>
+        <v>-15.2636</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7723</v>
+        <v>-17.7632</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-59.4683</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>41.7046</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3917</v>
+        <v>3.49</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1655</v>
+        <v>1.1331</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2261</v>
+        <v>2.3571</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>16.1961</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>28.0407</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-11.8447</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R. MARTIN RODRIGUEZ</t>
+          <t>J. MORENO CASTRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -874,76 +874,76 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="D6" t="n">
-        <v>-6.3708</v>
+        <v>-4.845699999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>-4.2155</v>
+        <v>1.1632</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.1553</v>
+        <v>-6.009100000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-4.2905</v>
+        <v>10.7723</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.7789</v>
+        <v>3.7488</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5116</v>
+        <v>7.0238</v>
       </c>
       <c r="J6" t="n">
-        <v>-3.4207</v>
+        <v>28.1601</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.4336</v>
+        <v>14.1706</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9871</v>
+        <v>13.9896</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.8698</v>
+        <v>-17.3877</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.3453</v>
+        <v>-10.422</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5245</v>
+        <v>-6.9658</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1931</v>
+        <v>-8.1089</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.5792</v>
+        <v>-26.8382</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3862</v>
+        <v>18.7288</v>
       </c>
       <c r="S6" t="n">
-        <v>1.2246</v>
+        <v>-3.1103</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4409</v>
+        <v>-1.9153</v>
       </c>
       <c r="U6" t="n">
-        <v>0.7838000000000001</v>
+        <v>-1.1952</v>
       </c>
       <c r="V6" t="n">
-        <v>-3.1118</v>
+        <v>-4.3985</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6565</v>
+        <v>1.7563</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.4554</v>
+        <v>-6.154800000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>S. SOW</t>
+          <t>R. MARTIN RODRIGUEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-10.1059</v>
+        <v>-7.3127</v>
       </c>
       <c r="E7" t="n">
-        <v>-4.8828</v>
+        <v>-4.8843</v>
       </c>
       <c r="F7" t="n">
-        <v>-5.223</v>
+        <v>-2.4284</v>
       </c>
       <c r="G7" t="n">
-        <v>-12.1742</v>
+        <v>-4.2905</v>
       </c>
       <c r="H7" t="n">
-        <v>-7.713500000000001</v>
+        <v>-1.7789</v>
       </c>
       <c r="I7" t="n">
-        <v>-4.4606</v>
+        <v>-2.5116</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.7137</v>
+        <v>-3.4207</v>
       </c>
       <c r="K7" t="n">
-        <v>-3.5726</v>
+        <v>-1.4336</v>
       </c>
       <c r="L7" t="n">
-        <v>0.8591</v>
+        <v>-1.9871</v>
       </c>
       <c r="M7" t="n">
-        <v>-9.4604</v>
+        <v>-0.8698</v>
       </c>
       <c r="N7" t="n">
-        <v>-4.1408</v>
+        <v>-0.3453</v>
       </c>
       <c r="O7" t="n">
-        <v>-5.3196</v>
+        <v>-0.5245</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.5447</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q7" t="n">
-        <v>-6.950900000000001</v>
+        <v>-0.5792</v>
       </c>
       <c r="R7" t="n">
-        <v>5.4062</v>
+        <v>0.3862</v>
       </c>
       <c r="S7" t="n">
-        <v>4.6777</v>
+        <v>0.2827</v>
       </c>
       <c r="T7" t="n">
-        <v>4.0526</v>
+        <v>-0.2279</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6251</v>
+        <v>0.5106000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0648</v>
+        <v>-3.1118</v>
       </c>
       <c r="W7" t="n">
-        <v>0.7289000000000001</v>
+        <v>-0.6565</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.7937</v>
+        <v>-2.4554</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. MORENO CASTRO</t>
+          <t>S. SOW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>-11.2422</v>
+        <v>-11.4877</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2091000000000003</v>
+        <v>-6.3169</v>
       </c>
       <c r="F8" t="n">
-        <v>-11.0331</v>
+        <v>-5.1706</v>
       </c>
       <c r="G8" t="n">
-        <v>10.7723</v>
+        <v>-12.1742</v>
       </c>
       <c r="H8" t="n">
-        <v>3.7488</v>
+        <v>-7.713500000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>7.0238</v>
+        <v>-4.4606</v>
       </c>
       <c r="J8" t="n">
-        <v>28.1601</v>
+        <v>-2.7137</v>
       </c>
       <c r="K8" t="n">
-        <v>14.1706</v>
+        <v>-3.5726</v>
       </c>
       <c r="L8" t="n">
-        <v>13.9896</v>
+        <v>0.8591</v>
       </c>
       <c r="M8" t="n">
-        <v>-17.3877</v>
+        <v>-9.4604</v>
       </c>
       <c r="N8" t="n">
-        <v>-10.422</v>
+        <v>-4.1408</v>
       </c>
       <c r="O8" t="n">
-        <v>-6.9658</v>
+        <v>-5.3196</v>
       </c>
       <c r="P8" t="n">
-        <v>-8.1089</v>
+        <v>-1.5447</v>
       </c>
       <c r="Q8" t="n">
-        <v>-26.8382</v>
+        <v>-6.950900000000001</v>
       </c>
       <c r="R8" t="n">
-        <v>18.7288</v>
+        <v>5.4062</v>
       </c>
       <c r="S8" t="n">
-        <v>-9.506500000000001</v>
+        <v>3.296</v>
       </c>
       <c r="T8" t="n">
-        <v>-3.2876</v>
+        <v>2.6183</v>
       </c>
       <c r="U8" t="n">
-        <v>-6.2192</v>
+        <v>0.6774</v>
       </c>
       <c r="V8" t="n">
-        <v>-4.3985</v>
+        <v>-1.0648</v>
       </c>
       <c r="W8" t="n">
-        <v>1.7563</v>
+        <v>0.7289000000000001</v>
       </c>
       <c r="X8" t="n">
-        <v>-6.154800000000001</v>
+        <v>-1.7937</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. HERNÁNDEZ CHÁVEZ</t>
+          <t>E. VIVANCOS ORTIZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>-11.9817</v>
+        <v>-13.1586</v>
       </c>
       <c r="E9" t="n">
-        <v>-14.7039</v>
+        <v>-2.444</v>
       </c>
       <c r="F9" t="n">
-        <v>2.7222</v>
+        <v>-10.7146</v>
       </c>
       <c r="G9" t="n">
-        <v>-9.8758</v>
+        <v>-5.5554</v>
       </c>
       <c r="H9" t="n">
-        <v>-7.3687</v>
+        <v>-5.4222</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.5073</v>
+        <v>-0.1333</v>
       </c>
       <c r="J9" t="n">
-        <v>-6.7226</v>
+        <v>4.0088</v>
       </c>
       <c r="K9" t="n">
-        <v>-1.2949</v>
+        <v>1.8225</v>
       </c>
       <c r="L9" t="n">
-        <v>-5.4276</v>
+        <v>2.1866</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1533</v>
+        <v>-9.564299999999999</v>
       </c>
       <c r="N9" t="n">
-        <v>-6.0736</v>
+        <v>-7.2445</v>
       </c>
       <c r="O9" t="n">
-        <v>2.9203</v>
+        <v>-2.3198</v>
       </c>
       <c r="P9" t="n">
-        <v>-4.633900000000001</v>
+        <v>0.7724</v>
       </c>
       <c r="Q9" t="n">
-        <v>-11.971</v>
+        <v>-5.9855</v>
       </c>
       <c r="R9" t="n">
-        <v>7.3371</v>
+        <v>6.7577</v>
       </c>
       <c r="S9" t="n">
-        <v>7.161</v>
+        <v>-2.9788</v>
       </c>
       <c r="T9" t="n">
-        <v>2.6169</v>
+        <v>-1.367</v>
       </c>
       <c r="U9" t="n">
-        <v>4.5441</v>
+        <v>-1.6118</v>
       </c>
       <c r="V9" t="n">
-        <v>-4.6328</v>
+        <v>-5.3968</v>
       </c>
       <c r="W9" t="n">
-        <v>1.3726</v>
+        <v>0.8994000000000001</v>
       </c>
       <c r="X9" t="n">
-        <v>-6.0054</v>
+        <v>-6.2962</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>E. VIVANCOS ORTIZ</t>
+          <t>R. HERNÁNDEZ CHÁVEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>-14.3666</v>
+        <v>-15.3498</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.5886</v>
+        <v>-16.9102</v>
       </c>
       <c r="F10" t="n">
-        <v>-10.778</v>
+        <v>1.5605</v>
       </c>
       <c r="G10" t="n">
-        <v>-5.5554</v>
+        <v>-9.8758</v>
       </c>
       <c r="H10" t="n">
-        <v>-5.4222</v>
+        <v>-7.3687</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.1333</v>
+        <v>-2.5073</v>
       </c>
       <c r="J10" t="n">
-        <v>4.0088</v>
+        <v>-6.7226</v>
       </c>
       <c r="K10" t="n">
-        <v>1.8225</v>
+        <v>-1.2949</v>
       </c>
       <c r="L10" t="n">
-        <v>2.1866</v>
+        <v>-5.4276</v>
       </c>
       <c r="M10" t="n">
-        <v>-9.564299999999999</v>
+        <v>-3.1533</v>
       </c>
       <c r="N10" t="n">
-        <v>-7.2445</v>
+        <v>-6.0736</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.3198</v>
+        <v>2.9203</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7724</v>
+        <v>-4.633900000000001</v>
       </c>
       <c r="Q10" t="n">
-        <v>-5.9855</v>
+        <v>-11.971</v>
       </c>
       <c r="R10" t="n">
-        <v>6.7577</v>
+        <v>7.3371</v>
       </c>
       <c r="S10" t="n">
-        <v>-4.1869</v>
+        <v>3.7928</v>
       </c>
       <c r="T10" t="n">
-        <v>-2.5115</v>
+        <v>0.4107000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.6752</v>
+        <v>3.3823</v>
       </c>
       <c r="V10" t="n">
-        <v>-5.3968</v>
+        <v>-4.6328</v>
       </c>
       <c r="W10" t="n">
-        <v>0.8994000000000001</v>
+        <v>1.3726</v>
       </c>
       <c r="X10" t="n">
-        <v>-6.2962</v>
+        <v>-6.0054</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-18.2754</v>
+        <v>-16.6878</v>
       </c>
       <c r="E11" t="n">
-        <v>-13.1975</v>
+        <v>-12.6803</v>
       </c>
       <c r="F11" t="n">
-        <v>-5.0778</v>
+        <v>-4.007400000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-4.6942</v>
@@ -1312,13 +1312,13 @@
         <v>3.0892</v>
       </c>
       <c r="S11" t="n">
-        <v>-3.7736</v>
+        <v>-2.1859</v>
       </c>
       <c r="T11" t="n">
-        <v>-2.2352</v>
+        <v>-1.7181</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.5384</v>
+        <v>-0.4679</v>
       </c>
       <c r="V11" t="n">
         <v>-2.0845</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>D. FLORES LUCAS</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>23</v>
       </c>
       <c r="D12" t="n">
-        <v>-24.5776</v>
+        <v>-20.0093</v>
       </c>
       <c r="E12" t="n">
-        <v>-12.3161</v>
+        <v>7.2699</v>
       </c>
       <c r="F12" t="n">
-        <v>-12.2614</v>
+        <v>-27.2792</v>
       </c>
       <c r="G12" t="n">
-        <v>-19.913</v>
+        <v>-5.579</v>
       </c>
       <c r="H12" t="n">
-        <v>-21.2168</v>
+        <v>-0.3250999999999996</v>
       </c>
       <c r="I12" t="n">
-        <v>1.303700000000001</v>
+        <v>-5.2542</v>
       </c>
       <c r="J12" t="n">
-        <v>-4.1243</v>
+        <v>35.4386</v>
       </c>
       <c r="K12" t="n">
-        <v>-5.207199999999999</v>
+        <v>32.2454</v>
       </c>
       <c r="L12" t="n">
-        <v>1.0833</v>
+        <v>3.1934</v>
       </c>
       <c r="M12" t="n">
-        <v>-15.7885</v>
+        <v>-41.018</v>
       </c>
       <c r="N12" t="n">
-        <v>-16.0091</v>
+        <v>-32.5704</v>
       </c>
       <c r="O12" t="n">
-        <v>0.2205000000000004</v>
+        <v>-8.4475</v>
       </c>
       <c r="P12" t="n">
-        <v>0.5792999999999999</v>
+        <v>-12.3569</v>
       </c>
       <c r="Q12" t="n">
-        <v>-15.8325</v>
+        <v>-48.0768</v>
       </c>
       <c r="R12" t="n">
-        <v>16.412</v>
+        <v>35.7196</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.6740999999999997</v>
+        <v>-1.3799</v>
       </c>
       <c r="T12" t="n">
-        <v>2.2009</v>
+        <v>-0.4515</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.8753</v>
+        <v>-0.9282999999999997</v>
       </c>
       <c r="V12" t="n">
-        <v>-4.569500000000001</v>
+        <v>-0.6931999999999996</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4393</v>
+        <v>20.3593</v>
       </c>
       <c r="X12" t="n">
-        <v>-10.009</v>
+        <v>-21.0523</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>A. BRASSEUR</t>
+          <t>D. FLORES LUCAS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="D13" t="n">
-        <v>-26.8875</v>
+        <v>-21.1045</v>
       </c>
       <c r="E13" t="n">
-        <v>-19.8256</v>
+        <v>-11.7921</v>
       </c>
       <c r="F13" t="n">
-        <v>-7.0619</v>
+        <v>-9.312100000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>-13.4204</v>
+        <v>-19.913</v>
       </c>
       <c r="H13" t="n">
-        <v>-8.6442</v>
+        <v>-21.2168</v>
       </c>
       <c r="I13" t="n">
-        <v>-4.7763</v>
+        <v>1.303700000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.322</v>
+        <v>-4.1243</v>
       </c>
       <c r="K13" t="n">
-        <v>2.3266</v>
+        <v>-5.207199999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>-2.6487</v>
+        <v>1.0833</v>
       </c>
       <c r="M13" t="n">
-        <v>-13.0983</v>
+        <v>-15.7885</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.9708</v>
+        <v>-16.0091</v>
       </c>
       <c r="O13" t="n">
-        <v>-2.1277</v>
+        <v>0.2205000000000004</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.8616</v>
+        <v>0.5792999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-14.674</v>
+        <v>-15.8325</v>
       </c>
       <c r="R13" t="n">
-        <v>10.8125</v>
+        <v>16.412</v>
       </c>
       <c r="S13" t="n">
-        <v>-6.4936</v>
+        <v>2.7989</v>
       </c>
       <c r="T13" t="n">
-        <v>-4.4159</v>
+        <v>2.7252</v>
       </c>
       <c r="U13" t="n">
-        <v>-2.0776</v>
+        <v>0.07399999999999995</v>
       </c>
       <c r="V13" t="n">
-        <v>-3.1119</v>
+        <v>-4.569500000000001</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.4134999999999999</v>
+        <v>5.4393</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.6984</v>
+        <v>-10.009</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. LUIS QUINTERO</t>
+          <t>A. BRASSEUR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
-        <v>-27.1701</v>
+        <v>-21.9529</v>
       </c>
       <c r="E14" t="n">
-        <v>-20.2597</v>
+        <v>-16.4329</v>
       </c>
       <c r="F14" t="n">
-        <v>-6.910100000000001</v>
+        <v>-5.5197</v>
       </c>
       <c r="G14" t="n">
-        <v>-24.7297</v>
+        <v>-13.4204</v>
       </c>
       <c r="H14" t="n">
-        <v>-18.62</v>
+        <v>-8.6442</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.109400000000001</v>
+        <v>-4.7763</v>
       </c>
       <c r="J14" t="n">
-        <v>13.6729</v>
+        <v>-0.322</v>
       </c>
       <c r="K14" t="n">
-        <v>8.9842</v>
+        <v>2.3266</v>
       </c>
       <c r="L14" t="n">
-        <v>4.689100000000002</v>
+        <v>-2.6487</v>
       </c>
       <c r="M14" t="n">
-        <v>-38.4026</v>
+        <v>-13.0983</v>
       </c>
       <c r="N14" t="n">
-        <v>-27.6039</v>
+        <v>-10.9708</v>
       </c>
       <c r="O14" t="n">
-        <v>-10.7984</v>
+        <v>-2.1277</v>
       </c>
       <c r="P14" t="n">
-        <v>-14.867</v>
+        <v>-3.8616</v>
       </c>
       <c r="Q14" t="n">
-        <v>-51.7451</v>
+        <v>-14.674</v>
       </c>
       <c r="R14" t="n">
-        <v>36.8779</v>
+        <v>10.8125</v>
       </c>
       <c r="S14" t="n">
-        <v>12.6642</v>
+        <v>-1.5587</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.7751</v>
+        <v>-1.0235</v>
       </c>
       <c r="U14" t="n">
-        <v>14.4398</v>
+        <v>-0.5350999999999999</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.2379000000000003</v>
+        <v>-3.1119</v>
       </c>
       <c r="W14" t="n">
-        <v>19.5876</v>
+        <v>-0.4134999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>-19.8255</v>
+        <v>-2.6984</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>M. DIAZ FELST</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D15" t="n">
-        <v>-28.676</v>
+        <v>-22.6284</v>
       </c>
       <c r="E15" t="n">
-        <v>2.360499999999999</v>
+        <v>-4.8828</v>
       </c>
       <c r="F15" t="n">
-        <v>-31.0366</v>
+        <v>-17.7455</v>
       </c>
       <c r="G15" t="n">
-        <v>-5.579</v>
+        <v>-19.433</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.3250999999999996</v>
+        <v>-13.7636</v>
       </c>
       <c r="I15" t="n">
-        <v>-5.2542</v>
+        <v>-5.669700000000001</v>
       </c>
       <c r="J15" t="n">
-        <v>35.4386</v>
+        <v>3.911799999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>32.2454</v>
+        <v>3.348</v>
       </c>
       <c r="L15" t="n">
-        <v>3.1934</v>
+        <v>0.5638000000000004</v>
       </c>
       <c r="M15" t="n">
-        <v>-41.018</v>
+        <v>-23.3445</v>
       </c>
       <c r="N15" t="n">
-        <v>-32.5704</v>
+        <v>-17.1113</v>
       </c>
       <c r="O15" t="n">
-        <v>-8.4475</v>
+        <v>-6.2334</v>
       </c>
       <c r="P15" t="n">
-        <v>-12.3569</v>
+        <v>3.2824</v>
       </c>
       <c r="Q15" t="n">
-        <v>-48.0768</v>
+        <v>-11.5849</v>
       </c>
       <c r="R15" t="n">
-        <v>35.7196</v>
+        <v>14.867</v>
       </c>
       <c r="S15" t="n">
-        <v>-10.0468</v>
+        <v>-5.0546</v>
       </c>
       <c r="T15" t="n">
-        <v>-5.3611</v>
+        <v>-2.9345</v>
       </c>
       <c r="U15" t="n">
-        <v>-4.6858</v>
+        <v>-2.1199</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.6931999999999996</v>
+        <v>-1.4228</v>
       </c>
       <c r="W15" t="n">
-        <v>20.3593</v>
+        <v>5.7249</v>
       </c>
       <c r="X15" t="n">
-        <v>-21.0523</v>
+        <v>-7.1478</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>M. DIAZ FELST</t>
+          <t>A. GOMEZ PEÑA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="D16" t="n">
-        <v>-29.5118</v>
+        <v>-24.1948</v>
       </c>
       <c r="E16" t="n">
-        <v>-8.627000000000001</v>
+        <v>-12.502</v>
       </c>
       <c r="F16" t="n">
-        <v>-20.885</v>
+        <v>-11.6927</v>
       </c>
       <c r="G16" t="n">
-        <v>-19.433</v>
+        <v>-9.313700000000001</v>
       </c>
       <c r="H16" t="n">
-        <v>-13.7636</v>
+        <v>-7.8309</v>
       </c>
       <c r="I16" t="n">
-        <v>-5.669700000000001</v>
+        <v>-1.4828</v>
       </c>
       <c r="J16" t="n">
-        <v>3.911799999999999</v>
+        <v>37.4796</v>
       </c>
       <c r="K16" t="n">
-        <v>3.348</v>
+        <v>25.5684</v>
       </c>
       <c r="L16" t="n">
-        <v>0.5638000000000004</v>
+        <v>11.9108</v>
       </c>
       <c r="M16" t="n">
-        <v>-23.3445</v>
+        <v>-46.7932</v>
       </c>
       <c r="N16" t="n">
-        <v>-17.1113</v>
+        <v>-33.3997</v>
       </c>
       <c r="O16" t="n">
-        <v>-6.2334</v>
+        <v>-13.3937</v>
       </c>
       <c r="P16" t="n">
-        <v>3.2824</v>
+        <v>-16.0254</v>
       </c>
       <c r="Q16" t="n">
-        <v>-11.5849</v>
+        <v>-56.3789</v>
       </c>
       <c r="R16" t="n">
-        <v>14.867</v>
+        <v>40.3532</v>
       </c>
       <c r="S16" t="n">
-        <v>-11.9383</v>
+        <v>-3.93</v>
       </c>
       <c r="T16" t="n">
-        <v>-6.678599999999999</v>
+        <v>-5.982</v>
       </c>
       <c r="U16" t="n">
-        <v>-5.2594</v>
+        <v>2.0518</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.4228</v>
+        <v>5.0744</v>
       </c>
       <c r="W16" t="n">
-        <v>5.7249</v>
+        <v>12.379</v>
       </c>
       <c r="X16" t="n">
-        <v>-7.1478</v>
+        <v>-7.3047</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. GONZALEZ-MONJE PEREZ</t>
+          <t>P. RODRIGUEZ FAJARDO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D17" t="n">
-        <v>-38.5457</v>
+        <v>-25.3809</v>
       </c>
       <c r="E17" t="n">
-        <v>-23.7064</v>
+        <v>-15.2604</v>
       </c>
       <c r="F17" t="n">
-        <v>-14.8396</v>
+        <v>-10.1207</v>
       </c>
       <c r="G17" t="n">
-        <v>-21.3613</v>
+        <v>-23.0938</v>
       </c>
       <c r="H17" t="n">
-        <v>-9.9815</v>
+        <v>-7.8309</v>
       </c>
       <c r="I17" t="n">
-        <v>-11.3799</v>
+        <v>-15.2632</v>
       </c>
       <c r="J17" t="n">
-        <v>0.2427000000000001</v>
+        <v>-0.3498999999999994</v>
       </c>
       <c r="K17" t="n">
-        <v>4.165899999999999</v>
+        <v>7.7659</v>
       </c>
       <c r="L17" t="n">
-        <v>-3.923299999999999</v>
+        <v>-8.116</v>
       </c>
       <c r="M17" t="n">
-        <v>-21.6042</v>
+        <v>-22.7437</v>
       </c>
       <c r="N17" t="n">
-        <v>-14.1473</v>
+        <v>-15.5968</v>
       </c>
       <c r="O17" t="n">
-        <v>-7.4568</v>
+        <v>-7.147</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.51</v>
+        <v>9.074900000000001</v>
       </c>
       <c r="Q17" t="n">
-        <v>-24.3281</v>
+        <v>-17.1841</v>
       </c>
       <c r="R17" t="n">
-        <v>21.818</v>
+        <v>26.2587</v>
       </c>
       <c r="S17" t="n">
-        <v>-2.095499999999999</v>
+        <v>-1.7938</v>
       </c>
       <c r="T17" t="n">
-        <v>-4.447</v>
+        <v>0.5177</v>
       </c>
       <c r="U17" t="n">
-        <v>2.3514</v>
+        <v>-2.3108</v>
       </c>
       <c r="V17" t="n">
-        <v>-12.5787</v>
+        <v>-9.568300000000001</v>
       </c>
       <c r="W17" t="n">
-        <v>4.8255</v>
+        <v>1.7563</v>
       </c>
       <c r="X17" t="n">
-        <v>-17.4042</v>
+        <v>-11.3246</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. RODRIGUEZ FAJARDO</t>
+          <t>C. LUIS QUINTERO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1810,76 +1810,76 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D18" t="n">
-        <v>-38.7314</v>
+        <v>-36.4954</v>
       </c>
       <c r="E18" t="n">
-        <v>-23.9758</v>
+        <v>-20.3147</v>
       </c>
       <c r="F18" t="n">
-        <v>-14.7555</v>
+        <v>-16.1808</v>
       </c>
       <c r="G18" t="n">
-        <v>-23.0938</v>
+        <v>-24.7297</v>
       </c>
       <c r="H18" t="n">
-        <v>-7.8309</v>
+        <v>-18.62</v>
       </c>
       <c r="I18" t="n">
-        <v>-15.2632</v>
+        <v>-6.109400000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3498999999999994</v>
+        <v>13.6729</v>
       </c>
       <c r="K18" t="n">
-        <v>7.7659</v>
+        <v>8.9842</v>
       </c>
       <c r="L18" t="n">
-        <v>-8.116</v>
+        <v>4.689100000000002</v>
       </c>
       <c r="M18" t="n">
-        <v>-22.7437</v>
+        <v>-38.4026</v>
       </c>
       <c r="N18" t="n">
-        <v>-15.5968</v>
+        <v>-27.6039</v>
       </c>
       <c r="O18" t="n">
-        <v>-7.147</v>
+        <v>-10.7984</v>
       </c>
       <c r="P18" t="n">
-        <v>9.074900000000001</v>
+        <v>-14.867</v>
       </c>
       <c r="Q18" t="n">
-        <v>-17.1841</v>
+        <v>-51.7451</v>
       </c>
       <c r="R18" t="n">
-        <v>26.2587</v>
+        <v>36.8779</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.144</v>
+        <v>3.3391</v>
       </c>
       <c r="T18" t="n">
-        <v>-8.197900000000001</v>
+        <v>-1.8304</v>
       </c>
       <c r="U18" t="n">
-        <v>-6.9459</v>
+        <v>5.1691</v>
       </c>
       <c r="V18" t="n">
-        <v>-9.568300000000001</v>
+        <v>-0.2379000000000003</v>
       </c>
       <c r="W18" t="n">
-        <v>1.7563</v>
+        <v>19.5876</v>
       </c>
       <c r="X18" t="n">
-        <v>-11.3246</v>
+        <v>-19.8255</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. GOMEZ PEÑA</t>
+          <t>M. GONZALEZ-MONJE PEREZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D19" t="n">
-        <v>-39.2508</v>
+        <v>-38.2632</v>
       </c>
       <c r="E19" t="n">
-        <v>-26.2233</v>
+        <v>-22.3617</v>
       </c>
       <c r="F19" t="n">
-        <v>-13.0275</v>
+        <v>-15.902</v>
       </c>
       <c r="G19" t="n">
-        <v>-9.313700000000001</v>
+        <v>-21.3613</v>
       </c>
       <c r="H19" t="n">
-        <v>-7.8309</v>
+        <v>-9.9815</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.4828</v>
+        <v>-11.3799</v>
       </c>
       <c r="J19" t="n">
-        <v>37.4796</v>
+        <v>0.2427000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>25.5684</v>
+        <v>4.165899999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>11.9108</v>
+        <v>-3.923299999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-46.7932</v>
+        <v>-21.6042</v>
       </c>
       <c r="N19" t="n">
-        <v>-33.3997</v>
+        <v>-14.1473</v>
       </c>
       <c r="O19" t="n">
-        <v>-13.3937</v>
+        <v>-7.4568</v>
       </c>
       <c r="P19" t="n">
-        <v>-16.0254</v>
+        <v>-2.51</v>
       </c>
       <c r="Q19" t="n">
-        <v>-56.3789</v>
+        <v>-24.3281</v>
       </c>
       <c r="R19" t="n">
-        <v>40.3532</v>
+        <v>21.818</v>
       </c>
       <c r="S19" t="n">
-        <v>-18.9859</v>
+        <v>-1.8132</v>
       </c>
       <c r="T19" t="n">
-        <v>-19.7032</v>
+        <v>-3.1022</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7171999999999999</v>
+        <v>1.2888</v>
       </c>
       <c r="V19" t="n">
-        <v>5.0744</v>
+        <v>-12.5787</v>
       </c>
       <c r="W19" t="n">
-        <v>12.379</v>
+        <v>4.8255</v>
       </c>
       <c r="X19" t="n">
-        <v>-7.3047</v>
+        <v>-17.4042</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>-290.4227</v>
+        <v>-274.3393</v>
       </c>
       <c r="E20" t="n">
-        <v>-109.8307</v>
+        <v>-102.7598</v>
       </c>
       <c r="F20" t="n">
-        <v>-180.5917</v>
+        <v>-171.5791</v>
       </c>
       <c r="G20" t="n">
         <v>-173.1235</v>
@@ -1996,7 +1996,7 @@
         <v>28.2701</v>
       </c>
       <c r="M20" t="n">
-        <v>-342.1362999999999</v>
+        <v>-342.1363</v>
       </c>
       <c r="N20" t="n">
         <v>-251.0493</v>
@@ -2014,16 +2014,16 @@
         <v>307.3813</v>
       </c>
       <c r="S20" t="n">
-        <v>-11.3059</v>
+        <v>4.777799999999999</v>
       </c>
       <c r="T20" t="n">
-        <v>-10.93</v>
+        <v>-3.859100000000001</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3754999999999989</v>
+        <v>8.637700000000001</v>
       </c>
       <c r="V20" t="n">
-        <v>-35.90560000000001</v>
+        <v>-35.9056</v>
       </c>
       <c r="W20" t="n">
         <v>109.5537</v>
